--- a/artfynd/A 37960-2025 artfynd.xlsx
+++ b/artfynd/A 37960-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88130803</v>
+        <v>88130810</v>
       </c>
       <c r="B2" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568126.1139956309</v>
+        <v>568317</v>
       </c>
       <c r="R2" t="n">
-        <v>7246779.842070388</v>
+        <v>7246599</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88130794</v>
+        <v>88130811</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568325.1406087197</v>
+        <v>568084</v>
       </c>
       <c r="R3" t="n">
-        <v>7246588.039264828</v>
+        <v>7246801</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88130807</v>
+        <v>88130789</v>
       </c>
       <c r="B4" t="n">
-        <v>89777</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,16 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568317.0000917999</v>
+        <v>568323</v>
       </c>
       <c r="R4" t="n">
-        <v>7246596.208744442</v>
+        <v>7246603</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -967,19 +937,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88130810</v>
+        <v>88130822</v>
       </c>
       <c r="B5" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568316.9320293418</v>
+        <v>568027</v>
       </c>
       <c r="R5" t="n">
-        <v>7246599.132795863</v>
+        <v>7246900</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1079,19 +1034,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88130793</v>
+        <v>88130799</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568323.1856793708</v>
+        <v>568303</v>
       </c>
       <c r="R6" t="n">
-        <v>7246582.142458723</v>
+        <v>7246622</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1191,19 +1131,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88130789</v>
+        <v>88130792</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568323.1176877413</v>
+        <v>568156</v>
       </c>
       <c r="R7" t="n">
-        <v>7246603.038312075</v>
+        <v>7246648</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1303,19 +1228,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88130799</v>
+        <v>88130793</v>
       </c>
       <c r="B8" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568303.0145848618</v>
+        <v>568323</v>
       </c>
       <c r="R8" t="n">
-        <v>7246621.795909166</v>
+        <v>7246582</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1415,19 +1325,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88130811</v>
+        <v>88130803</v>
       </c>
       <c r="B9" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568084.2000121765</v>
+        <v>568126</v>
       </c>
       <c r="R9" t="n">
-        <v>7246801.019105757</v>
+        <v>7246780</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1527,19 +1422,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88130804</v>
+        <v>88130794</v>
       </c>
       <c r="B10" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568162.0017218329</v>
+        <v>568325</v>
       </c>
       <c r="R10" t="n">
-        <v>7246639.832672998</v>
+        <v>7246588</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1639,19 +1519,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>88130792</v>
+        <v>88130804</v>
       </c>
       <c r="B11" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568155.9528340185</v>
+        <v>568162</v>
       </c>
       <c r="R11" t="n">
-        <v>7246648.051002088</v>
+        <v>7246640</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1751,19 +1616,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1787,6 +1642,204 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>80085211</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Betesberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>568266</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7246459</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2019-09-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2019-09-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>88130807</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Brattberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>568317</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7246596</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Per-Anders Blomqvist, Henrik Sporrong</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
